--- a/db/funcs/T_SWCTRL.xlsx
+++ b/db/funcs/T_SWCTRL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="28290" windowHeight="12585"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="28290" windowHeight="12585" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Controls" sheetId="4" r:id="rId1"/>
@@ -710,9 +710,6 @@
     <t>CBCSWI1.Health</t>
   </si>
   <si>
-    <t>SWCTRL_EnaDis</t>
-  </si>
-  <si>
     <t>CBCSWI1_EnaDis</t>
   </si>
   <si>
@@ -804,6 +801,9 @@
   </si>
   <si>
     <t>Выдержка времени подавления выдачи положения «Не определено»</t>
+  </si>
+  <si>
+    <t>LLN0_EnaDis</t>
   </si>
 </sst>
 </file>
@@ -1915,13 +1915,13 @@
         <v>38</v>
       </c>
       <c r="AV2" s="95" t="s">
+        <v>248</v>
+      </c>
+      <c r="AW2" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="AW2" s="95" t="s">
+      <c r="AX2" s="95" t="s">
         <v>250</v>
-      </c>
-      <c r="AX2" s="95" t="s">
-        <v>251</v>
       </c>
       <c r="AY2" s="42"/>
       <c r="AZ2" s="41" t="s">
@@ -18272,7 +18272,7 @@
     <row r="3" spans="1:16379" s="119" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="106"/>
       <c r="B3" s="106" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C3" s="107"/>
       <c r="D3" s="108"/>
@@ -18393,7 +18393,7 @@
     <row r="4" spans="1:16379" s="119" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="106"/>
       <c r="B4" s="106" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C4" s="107"/>
       <c r="D4" s="120" t="s">
@@ -18639,7 +18639,7 @@
     <row r="6" spans="1:16379" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="50"/>
       <c r="B6" s="94" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="24"/>
@@ -18885,7 +18885,7 @@
     <row r="8" spans="1:16379" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="50"/>
       <c r="B8" s="94" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C8" s="51"/>
       <c r="D8" s="24"/>
@@ -19254,18 +19254,18 @@
     <row r="11" spans="1:16379" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="50"/>
       <c r="B11" s="94" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C11" s="51"/>
       <c r="D11" s="24"/>
       <c r="E11" s="101" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F11" s="102" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G11" s="102" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H11" s="53"/>
       <c r="I11" s="53">
@@ -19377,7 +19377,7 @@
     <row r="12" spans="1:16379" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="50"/>
       <c r="B12" s="94" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C12" s="51"/>
       <c r="D12" s="24"/>
@@ -19623,7 +19623,7 @@
     <row r="14" spans="1:16379" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="50"/>
       <c r="B14" s="94" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C14" s="51"/>
       <c r="D14" s="24"/>
@@ -20238,7 +20238,7 @@
     <row r="19" spans="1:60" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="50"/>
       <c r="B19" s="94" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C19" s="51"/>
       <c r="D19" s="24"/>
@@ -20361,7 +20361,7 @@
     <row r="20" spans="1:60" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="50"/>
       <c r="B20" s="94" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C20" s="51"/>
       <c r="D20" s="24"/>
@@ -27272,13 +27272,13 @@
         <v>38</v>
       </c>
       <c r="AV2" s="95" t="s">
+        <v>248</v>
+      </c>
+      <c r="AW2" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="AW2" s="95" t="s">
+      <c r="AX2" s="95" t="s">
         <v>250</v>
-      </c>
-      <c r="AX2" s="95" t="s">
-        <v>251</v>
       </c>
       <c r="AY2" s="42"/>
       <c r="AZ2" s="41" t="s">
@@ -43629,7 +43629,7 @@
     <row r="3" spans="1:16379" s="92" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="75"/>
       <c r="B3" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C3" s="83"/>
       <c r="D3" s="77" t="s">
@@ -43753,7 +43753,7 @@
     <row r="4" spans="1:16379" s="92" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="75"/>
       <c r="B4" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C4" s="83"/>
       <c r="D4" s="77" t="s">
@@ -43877,7 +43877,7 @@
     <row r="5" spans="1:16379" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="64"/>
       <c r="B5" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C5" s="65"/>
       <c r="D5" s="24" t="s">
@@ -43999,7 +43999,7 @@
     <row r="6" spans="1:16379" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="64"/>
       <c r="B6" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C6" s="65"/>
       <c r="D6" s="24" t="s">
@@ -44138,7 +44138,7 @@
     <row r="7" spans="1:16379" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="64"/>
       <c r="B7" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C7" s="65"/>
       <c r="D7" s="24" t="s">
@@ -44277,7 +44277,7 @@
     <row r="8" spans="1:16379" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="64"/>
       <c r="B8" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C8" s="65"/>
       <c r="D8" s="24" t="s">
@@ -44399,7 +44399,7 @@
     <row r="9" spans="1:16379" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="64"/>
       <c r="B9" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C9" s="65"/>
       <c r="D9" s="24" t="s">
@@ -44538,7 +44538,7 @@
     <row r="10" spans="1:16379" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="64"/>
       <c r="B10" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C10" s="65"/>
       <c r="D10" s="24" t="s">
@@ -44660,7 +44660,7 @@
     <row r="11" spans="1:16379" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="64"/>
       <c r="B11" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C11" s="65"/>
       <c r="D11" s="24" t="s">
@@ -44782,7 +44782,7 @@
     <row r="12" spans="1:16379" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="64"/>
       <c r="B12" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C12" s="65"/>
       <c r="D12" s="24" t="s">
@@ -44904,7 +44904,7 @@
     <row r="13" spans="1:16379" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="64"/>
       <c r="B13" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C13" s="65"/>
       <c r="D13" s="24" t="s">
@@ -45026,7 +45026,7 @@
     <row r="14" spans="1:16379" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="7"/>
@@ -45167,7 +45167,7 @@
     <row r="15" spans="1:16379" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="13"/>
@@ -45308,7 +45308,7 @@
     <row r="16" spans="1:16379" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="64"/>
       <c r="B16" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C16" s="65"/>
       <c r="D16" s="24" t="s">
@@ -45447,7 +45447,7 @@
     <row r="17" spans="1:60" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="64"/>
       <c r="B17" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C17" s="65"/>
       <c r="D17" s="24" t="s">
@@ -45586,7 +45586,7 @@
     <row r="18" spans="1:60" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="64"/>
       <c r="B18" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C18" s="65"/>
       <c r="D18" s="24" t="s">
@@ -45725,7 +45725,7 @@
     <row r="19" spans="1:60" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="64"/>
       <c r="B19" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C19" s="65"/>
       <c r="D19" s="24" t="s">
@@ -45867,7 +45867,7 @@
     <row r="20" spans="1:60" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="7" t="s">
@@ -46010,7 +46010,7 @@
     <row r="21" spans="1:60" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="7" t="s">
@@ -46290,7 +46290,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="103" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I2" s="38" t="s">
         <v>7</v>
@@ -62799,8 +62799,8 @@
         <f>IF(LEN(F3)&lt;=$K$1,F3,"")</f>
         <v>Ввод_функции</v>
       </c>
-      <c r="L3" s="75" t="s">
-        <v>229</v>
+      <c r="L3" s="96" t="s">
+        <v>260</v>
       </c>
       <c r="M3" s="87" t="s">
         <v>54</v>
@@ -62854,7 +62854,7 @@
         <v>0</v>
       </c>
       <c r="AJ3" s="99" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AK3" s="83"/>
       <c r="AL3" s="83"/>
@@ -62930,7 +62930,7 @@
         <v>Ввод_функции</v>
       </c>
       <c r="L4" s="64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M4" s="67" t="s">
         <v>54</v>
@@ -63035,10 +63035,10 @@
         <v>210</v>
       </c>
       <c r="E5" s="63" t="s">
+        <v>233</v>
+      </c>
+      <c r="F5" s="63" t="s">
         <v>234</v>
-      </c>
-      <c r="F5" s="63" t="s">
-        <v>235</v>
       </c>
       <c r="G5" s="63" t="s">
         <v>115</v>
@@ -63058,7 +63058,7 @@
         <v>Бл_вкл_от_авар_откл</v>
       </c>
       <c r="L5" s="64" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M5" s="67" t="s">
         <v>54</v>
@@ -63163,16 +63163,16 @@
         <v>210</v>
       </c>
       <c r="E6" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="F6" s="63" t="s">
         <v>236</v>
       </c>
-      <c r="F6" s="63" t="s">
+      <c r="G6" s="63" t="s">
         <v>237</v>
       </c>
-      <c r="G6" s="63" t="s">
-        <v>238</v>
-      </c>
       <c r="H6" s="105" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I6" s="63"/>
       <c r="J6" s="63">
@@ -63184,7 +63184,7 @@
         <v>Tперекл</v>
       </c>
       <c r="L6" s="64" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M6" s="67" t="s">
         <v>112</v>
@@ -63243,10 +63243,10 @@
         <v>216</v>
       </c>
       <c r="AK6" s="59" t="s">
+        <v>240</v>
+      </c>
+      <c r="AL6" s="59" t="s">
         <v>241</v>
-      </c>
-      <c r="AL6" s="59" t="s">
-        <v>242</v>
       </c>
       <c r="AM6" s="59" t="s">
         <v>116</v>
@@ -63256,7 +63256,7 @@
       </c>
       <c r="AO6" s="59"/>
       <c r="AP6" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AQ6" s="59" t="str">
         <f>CONCATENATE(AK6, ".", AM6)</f>
@@ -63306,16 +63306,16 @@
         <v>210</v>
       </c>
       <c r="E7" s="100" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F7" s="63" t="s">
+        <v>238</v>
+      </c>
+      <c r="G7" s="63" t="s">
         <v>239</v>
       </c>
-      <c r="G7" s="63" t="s">
-        <v>240</v>
-      </c>
       <c r="H7" s="105" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I7" s="63"/>
       <c r="J7" s="63">
@@ -63327,7 +63327,7 @@
         <v>Tблк</v>
       </c>
       <c r="L7" s="64" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M7" s="67" t="s">
         <v>112</v>
@@ -63386,10 +63386,10 @@
         <v>216</v>
       </c>
       <c r="AK7" s="59" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AL7" s="59" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AM7" s="59" t="s">
         <v>116</v>
@@ -63399,7 +63399,7 @@
       </c>
       <c r="AO7" s="59"/>
       <c r="AP7" s="59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AQ7" s="59" t="str">
         <f>CONCATENATE(AK7, ".", AM7)</f>
@@ -63495,12 +63495,12 @@
         <v>91</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="48" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B7" s="47">
         <v>2</v>
@@ -63508,15 +63508,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="98" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B9" s="98"/>
     </row>
@@ -63525,7 +63525,7 @@
         <v>174</v>
       </c>
       <c r="B10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -63533,12 +63533,12 @@
         <v>210</v>
       </c>
       <c r="B11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B12" s="98"/>
     </row>
